--- a/code_automated_correlation/raw_data/20250131-densitycutter.xlsx
+++ b/code_automated_correlation/raw_data/20250131-densitycutter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jille\Documents\Uni\Master-Mechatronik\Masterarbeit\SMP-SignalProcessing\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jille\Documents\Uni\Master-Mechatronik\Masterarbeit\SMP-SignalProcessing\code_automated_correlation\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FE3B28-621B-4CD6-954C-875E84E334D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFC47A2-1859-4058-AC2F-B906CC6B1DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26160" yWindow="1695" windowWidth="21600" windowHeight="10365" xr2:uid="{61D6FC73-02F6-43A9-80E2-DF36798766F6}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{61D6FC73-02F6-43A9-80E2-DF36798766F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -437,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C8E1CA8-A778-4AE0-A87F-1DE4A1FF0877}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -474,10 +474,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C2">
         <v>117</v>
@@ -486,7 +486,7 @@
         <v>113</v>
       </c>
       <c r="G2">
-        <f t="shared" ref="G2:G11" si="0">ABS(D2 - C2) / C2 * 100</f>
+        <f>ABS(D2 - C2) / C2 * 100</f>
         <v>3.4188034188034191</v>
       </c>
       <c r="I2">
@@ -496,206 +496,184 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B3">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="C3">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="D3">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="G3">
-        <f t="shared" si="0"/>
-        <v>3.4188034188034191</v>
+        <f>ABS(D3 - C3) / C3 * 100</f>
+        <v>1.3888888888888888</v>
       </c>
       <c r="I3">
         <f>AVERAGE(C3:E3)</f>
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B4">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C4">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="D4">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="G4">
-        <f t="shared" si="0"/>
-        <v>1.3888888888888888</v>
+        <f>ABS(D4 - C4) / C4 * 100</f>
+        <v>1.1235955056179776</v>
       </c>
       <c r="I4">
         <f>AVERAGE(C4:E4)</f>
-        <v>145</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B5">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5">
-        <v>178</v>
+        <v>288</v>
       </c>
       <c r="D5">
-        <v>180</v>
+        <v>279</v>
+      </c>
+      <c r="E5">
+        <v>280</v>
       </c>
       <c r="G5">
-        <f t="shared" si="0"/>
-        <v>1.1235955056179776</v>
+        <f>ABS(D5 - C5) / C5 * 100</f>
+        <v>3.125</v>
+      </c>
+      <c r="H5">
+        <f>ABS(E5 - C5) / C5 * 100</f>
+        <v>2.7777777777777777</v>
       </c>
       <c r="I5">
         <f>AVERAGE(C5:E5)</f>
-        <v>179</v>
+        <v>282.33333333333331</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="B6">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C6">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="D6">
-        <v>279</v>
-      </c>
-      <c r="E6">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G6">
-        <f t="shared" si="0"/>
-        <v>3.125</v>
-      </c>
-      <c r="H6">
-        <f>ABS(E6 - C6) / C6 * 100</f>
-        <v>2.7777777777777777</v>
+        <f>ABS(D6 - C6) / C6 * 100</f>
+        <v>1.1235955056179776</v>
       </c>
       <c r="I6">
-        <f>AVERAGE(C6:E6)</f>
-        <v>282.33333333333331</v>
+        <f>AVERAGE(C6:D6)</f>
+        <v>268.5</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C7">
-        <v>267</v>
+        <v>311</v>
       </c>
       <c r="D7">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="G7">
-        <f t="shared" si="0"/>
-        <v>1.1235955056179776</v>
+        <f>ABS(D7 - C7) / C7 * 100</f>
+        <v>0.32154340836012862</v>
       </c>
       <c r="I7">
         <f>AVERAGE(C7:D7)</f>
-        <v>268.5</v>
+        <v>311.5</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C8">
-        <v>311</v>
+        <v>363</v>
       </c>
       <c r="D8">
-        <v>312</v>
+        <v>363</v>
       </c>
       <c r="G8">
-        <f t="shared" si="0"/>
-        <v>0.32154340836012862</v>
+        <f>ABS(D8 - C8) / C8 * 100</f>
+        <v>0</v>
       </c>
       <c r="I8">
         <f>AVERAGE(C8:D8)</f>
-        <v>311.5</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B9">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C9">
-        <v>363</v>
+        <v>287</v>
       </c>
       <c r="D9">
-        <v>363</v>
+        <v>294</v>
       </c>
       <c r="G9">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>ABS(D9 - C9) / C9 * 100</f>
+        <v>2.4390243902439024</v>
       </c>
       <c r="I9">
         <f>AVERAGE(C9:D9)</f>
-        <v>363</v>
+        <v>290.5</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="B10">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D10">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="G10">
-        <f t="shared" si="0"/>
-        <v>2.4390243902439024</v>
+        <f>ABS(D10 - C10) / C10 * 100</f>
+        <v>0.69930069930069927</v>
       </c>
       <c r="I10">
         <f>AVERAGE(C10:D10)</f>
-        <v>290.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>118</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>286</v>
-      </c>
-      <c r="D11">
-        <v>288</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>0.69930069930069927</v>
-      </c>
-      <c r="I11">
-        <f>AVERAGE(C11:D11)</f>
         <v>287</v>
       </c>
     </row>
